--- a/data/trans_camb/P16A_n_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,58</t>
+          <t>-0,26; 4,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,99</t>
+          <t>-0,33; 3,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,21</t>
+          <t>0,05; 3,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,73</t>
+          <t>-3,25; 2,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,22</t>
+          <t>-2,81; 3,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,66</t>
+          <t>-1,92; 3,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,66</t>
+          <t>-0,99; 2,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,51</t>
+          <t>-1,01; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,91</t>
+          <t>-0,35; 2,85</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-70,82; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,67; —</t>
+          <t>-52,02; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,18; 215,12</t>
+          <t>-69,14; 198,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 242,7</t>
+          <t>-67,6; 221,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 296,61</t>
+          <t>-42,65; 255,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 276,76</t>
+          <t>-39,01; 278,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 275,0</t>
+          <t>-45,89; 236,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 305,47</t>
+          <t>-17,52; 306,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,33</t>
+          <t>0,73; 5,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,85</t>
+          <t>-1,24; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,69</t>
+          <t>0,66; 4,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,34</t>
+          <t>-0,3; 5,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,79</t>
+          <t>-2,94; 1,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,84</t>
+          <t>1,18; 6,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,39</t>
+          <t>0,82; 4,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,47</t>
+          <t>-1,56; 1,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,77</t>
+          <t>1,24; 4,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 842,27</t>
+          <t>9,86; 802,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,53; 315,82</t>
+          <t>-63,86; 336,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 717,82</t>
+          <t>2,72; 827,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 183,58</t>
+          <t>-8,52; 203,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 65,89</t>
+          <t>-57,05; 63,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,44; 203,27</t>
+          <t>20,99; 225,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,55; 225,54</t>
+          <t>19,9; 229,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 79,72</t>
+          <t>-46,4; 79,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,49; 245,59</t>
+          <t>36,43; 249,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,25</t>
+          <t>-0,6; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,99</t>
+          <t>-0,66; 0,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,73</t>
+          <t>4,7; 9,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,47</t>
+          <t>0,6; 3,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,05</t>
+          <t>0,77; 3,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 16,48</t>
+          <t>10,94; 16,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,17; 1,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,33</t>
+          <t>0,36; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,54</t>
+          <t>8,32; 12,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,26</t>
+          <t>-0,83; 2,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,51</t>
+          <t>0,2; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,18</t>
+          <t>2,72; 8,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,17</t>
+          <t>2,9; 9,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,32</t>
+          <t>2,57; 8,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,45</t>
+          <t>0,97; 6,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,86</t>
+          <t>1,53; 5,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,44</t>
+          <t>1,64; 5,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,32</t>
+          <t>2,64; 6,45</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 1598,37</t>
+          <t>-34,26; 1434,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111,84; 3359,14</t>
+          <t>134,88; 3233,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,68; 780,5</t>
+          <t>74,84; 866,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,67; 686,6</t>
+          <t>71,41; 804,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,43; 552,03</t>
+          <t>31,35; 565,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,44; 563,99</t>
+          <t>64,53; 565,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78,29; 629,32</t>
+          <t>61,13; 590,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>108,05; 736,12</t>
+          <t>106,65; 724,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,41</t>
+          <t>1,64; 8,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,95</t>
+          <t>-0,49; 3,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,42</t>
+          <t>3,54; 9,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 18,27</t>
+          <t>7,42; 18,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,88</t>
+          <t>-0,48; 6,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 13,12</t>
+          <t>2,78; 13,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,49; 11,63</t>
+          <t>5,61; 12,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,99</t>
+          <t>0,08; 3,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,58</t>
+          <t>4,78; 10,44</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144,44; 2352,12</t>
+          <t>162,21; 2647,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 897,32</t>
+          <t>-33,31; 1035,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>106,85; 2319,17</t>
+          <t>59,72; 1676,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>212,64; 2175,57</t>
+          <t>227,69; 2659,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 759,35</t>
+          <t>-7,29; 900,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>201,3; 1980,99</t>
+          <t>216,11; 2133,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,57</t>
+          <t>-1,24; 1,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,19</t>
+          <t>0,03; 4,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,69; 12,42</t>
+          <t>6,72; 12,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,36</t>
+          <t>-0,98; 3,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,04</t>
+          <t>2,17; 8,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,82; 14,91</t>
+          <t>8,98; 15,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,91</t>
+          <t>-0,69; 2,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,71</t>
+          <t>1,56; 5,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,99</t>
+          <t>8,75; 12,85</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,63; —</t>
+          <t>-54,86; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>301,01; —</t>
+          <t>279,34; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,11; 1181,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>67,94; 2376,66</t>
+          <t>44,07; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>308,75; 3995,82</t>
+          <t>251,71; 4153,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 482,61</t>
+          <t>-60,79; 609,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>84,85; 1481,9</t>
+          <t>59,48; 1485,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>448,69; 3472,25</t>
+          <t>475,69; 3542,61</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,86</t>
+          <t>-2,13; 0,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,12</t>
+          <t>-1,43; 2,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,78</t>
+          <t>-0,56; 2,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,65</t>
+          <t>-0,81; 2,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,08</t>
+          <t>-0,45; 2,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,2</t>
+          <t>1,88; 9,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,25</t>
+          <t>-0,95; 1,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,09</t>
+          <t>-0,49; 2,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,51</t>
+          <t>1,49; 5,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 72,67</t>
+          <t>-71,97; 69,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 161,88</t>
+          <t>-49,42; 169,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 205,22</t>
+          <t>-24,93; 206,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 212,86</t>
+          <t>-30,37; 192,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 253,19</t>
+          <t>-22,52; 236,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>65,24; 614,93</t>
+          <t>77,01; 660,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,81; 85,63</t>
+          <t>-40,09; 89,98</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 135,45</t>
+          <t>-20,25; 143,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>64,44; 353,7</t>
+          <t>76,52; 380,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,26</t>
+          <t>-3,45; -0,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,82</t>
+          <t>-3,64; -0,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,49</t>
+          <t>-2,12; 2,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,37</t>
+          <t>-1,27; 3,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,31</t>
+          <t>-1,1; 3,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,81</t>
+          <t>3,72; 8,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,0</t>
+          <t>-1,67; 0,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,91</t>
+          <t>-1,69; 0,82</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,73</t>
+          <t>0,01; 4,7</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-86,06; -4,08</t>
+          <t>-86,44; 1,18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-89,32; -22,66</t>
+          <t>-91,35; -23,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 109,97</t>
+          <t>-52,73; 111,57</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 114,61</t>
+          <t>-26,32; 106,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 104,4</t>
+          <t>-23,43; 103,79</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>65,62; 284,79</t>
+          <t>66,18; 293,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 36,01</t>
+          <t>-40,5; 35,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 32,68</t>
+          <t>-41,25; 29,67</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,51; 155,72</t>
+          <t>5,39; 160,87</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,96</t>
+          <t>-0,36; 0,97</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,77</t>
+          <t>-0,42; 0,8</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,93</t>
+          <t>1,93; 3,81</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,36</t>
+          <t>1,43; 3,33</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,58</t>
+          <t>0,86; 2,67</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,41</t>
+          <t>4,43; 7,4</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,95</t>
+          <t>0,82; 1,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,53</t>
+          <t>0,45; 1,57</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,53</t>
+          <t>3,83; 5,48</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 79,86</t>
+          <t>-22,12; 80,19</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 64,82</t>
+          <t>-23,26; 67,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>116,41; 317,29</t>
+          <t>114,76; 338,13</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>52,76; 155,56</t>
+          <t>48,5; 153,73</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>28,95; 119,1</t>
+          <t>28,45; 119,01</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>166,55; 345,22</t>
+          <t>159,65; 341,34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>35,32; 109,53</t>
+          <t>34,84; 110,5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>18,25; 87,22</t>
+          <t>17,68; 88,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>170,7; 309,75</t>
+          <t>171,64; 301,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,77</t>
+          <t>0,04; 4,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,1</t>
+          <t>-0,18; 3,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,38</t>
+          <t>-0,08; 3,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,64</t>
+          <t>-3,02; 2,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,26</t>
+          <t>-2,83; 2,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,44</t>
+          <t>-2,16; 2,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,61</t>
+          <t>-0,98; 2,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,49</t>
+          <t>-1,01; 2,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,85</t>
+          <t>-0,55; 2,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238,31%</t>
+          <t>245,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,02; —</t>
+          <t>-42,14; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 198,12</t>
+          <t>-67,95; 251,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 221,3</t>
+          <t>-68,34; 203,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 255,12</t>
+          <t>-48,96; 213,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 278,14</t>
+          <t>-42,61; 249,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 236,15</t>
+          <t>-42,34; 240,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 306,42</t>
+          <t>-26,29; 253,38</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>2,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,27</t>
+          <t>0,62; 5,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,73</t>
+          <t>-1,13; 1,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,62</t>
+          <t>0,89; 4,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,53</t>
+          <t>-0,4; 5,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,62</t>
+          <t>-2,88; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,14</t>
+          <t>0,42; 5,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,45</t>
+          <t>0,8; 4,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,45</t>
+          <t>-1,64; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,66</t>
+          <t>1,26; 4,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197,39%</t>
+          <t>198,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113,39%</t>
+          <t>111,29%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 802,3</t>
+          <t>16,81; 974,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,86; 336,13</t>
+          <t>-62,87; 344,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 827,37</t>
+          <t>23,11; 765,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 203,04</t>
+          <t>-7,85; 198,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,05; 63,55</t>
+          <t>-56,78; 68,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 225,76</t>
+          <t>6,57; 201,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 229,05</t>
+          <t>21,08; 234,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 79,09</t>
+          <t>-47,94; 71,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,43; 249,88</t>
+          <t>35,95; 234,19</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,59</t>
+          <t>13,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>10,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,97</t>
+          <t>-0,6; 0,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,98</t>
+          <t>-0,66; 1,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 9,63</t>
+          <t>4,5; 9,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,67</t>
+          <t>0,62; 3,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,91</t>
+          <t>0,76; 4,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,61</t>
+          <t>11,07; 16,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,9</t>
+          <t>0,16; 1,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,23</t>
+          <t>0,34; 2,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 12,3</t>
+          <t>8,46; 12,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2285,11%</t>
+          <t>2243,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7141,13%</t>
+          <t>7097,74%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,04</t>
+          <t>-0,74; 2,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,55</t>
+          <t>0,23; 3,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,01</t>
+          <t>2,45; 7,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,21</t>
+          <t>2,97; 9,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,76</t>
+          <t>2,13; 8,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,59</t>
+          <t>2,67; 7,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,01</t>
+          <t>1,44; 5,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,41</t>
+          <t>1,96; 5,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,45</t>
+          <t>3,4; 6,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>670,16%</t>
+          <t>616,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185,62%</t>
+          <t>241,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>309,58%</t>
+          <t>338,4%</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 1434,4</t>
+          <t>-17,94; 1604,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>134,88; 3233,65</t>
+          <t>134,73; 2760,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,84; 866,12</t>
+          <t>68,02; 778,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,41; 804,83</t>
+          <t>61,46; 816,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,35; 565,42</t>
+          <t>69,18; 676,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,53; 565,94</t>
+          <t>61,87; 634,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>61,13; 590,15</t>
+          <t>87,33; 628,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>106,65; 724,61</t>
+          <t>144,74; 878,93</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,23</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>8,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,15</t>
+          <t>1,55; 7,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,08</t>
+          <t>-0,48; 3,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,45</t>
+          <t>3,07; 8,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 18,03</t>
+          <t>7,71; 17,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 6,93</t>
+          <t>-0,38; 6,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 13,29</t>
+          <t>7,65; 14,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,05</t>
+          <t>5,51; 11,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,94</t>
+          <t>-0,07; 3,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,44</t>
+          <t>6,39; 10,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1355,6%</t>
+          <t>1217,13%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>464,35%</t>
+          <t>559,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>656,3%</t>
+          <t>688,6%</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162,21; 2647,77</t>
+          <t>131,55; 2588,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 1035,63</t>
+          <t>-28,34; 1064,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,72; 1676,22</t>
+          <t>178,84; 2625,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>227,69; 2659,92</t>
+          <t>220,21; 2180,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 900,18</t>
+          <t>-20,27; 761,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>216,11; 2133,95</t>
+          <t>241,45; 2069,99</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,67</t>
+          <t>10,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,56</t>
+          <t>-1,22; 1,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,21</t>
+          <t>0,06; 4,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,65</t>
+          <t>6,7; 12,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,63</t>
+          <t>-0,98; 3,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,66</t>
+          <t>1,91; 8,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,98; 15,11</t>
+          <t>9,08; 15,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,08</t>
+          <t>-0,61; 1,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,7</t>
+          <t>1,55; 5,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,85</t>
+          <t>8,59; 12,75</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1462,32%</t>
+          <t>1435,17%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1086,48%</t>
+          <t>1098,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1218,46%</t>
+          <t>1217,1%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-54,86; —</t>
+          <t>-50,1; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>279,34; —</t>
+          <t>318,58; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 1181,73</t>
+          <t>-74,1; 1021,08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44,07; —</t>
+          <t>37,36; 2086,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>251,71; 4153,63</t>
+          <t>335,02; 4095,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 609,11</t>
+          <t>-57,72; 621,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>59,48; 1485,01</t>
+          <t>76,75; 1637,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475,69; 3542,61</t>
+          <t>466,95; 3591,28</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>8,84</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,84</t>
+          <t>-2,2; 0,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,25</t>
+          <t>-1,25; 2,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,84</t>
+          <t>-0,74; 3,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,57</t>
+          <t>-0,75; 2,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,98</t>
+          <t>-0,42; 2,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,3</t>
+          <t>6,63; 10,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,37</t>
+          <t>-1,06; 1,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,08</t>
+          <t>-0,38; 2,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,64</t>
+          <t>3,83; 6,54</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>308,67%</t>
+          <t>450,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>193,85%</t>
+          <t>253,55%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-71,97; 69,79</t>
+          <t>-70,79; 84,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 169,18</t>
+          <t>-45,31; 155,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 206,64</t>
+          <t>-24,15; 226,25</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 192,7</t>
+          <t>-32,05; 220,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 236,76</t>
+          <t>-22,7; 234,78</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>77,01; 660,37</t>
+          <t>221,73; 926,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 89,98</t>
+          <t>-39,62; 77,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 143,75</t>
+          <t>-14,29; 130,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>76,52; 380,48</t>
+          <t>135,07; 429,28</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3,52</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,37</t>
+          <t>-3,17; -0,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,81</t>
+          <t>-3,52; -0,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,48</t>
+          <t>-0,22; 3,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,21</t>
+          <t>-1,29; 3,08</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,18</t>
+          <t>-1,13; 3,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,99</t>
+          <t>3,17; 7,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,98</t>
+          <t>-1,68; 0,91</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,82</t>
+          <t>-1,86; 0,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,7</t>
+          <t>2,13; 4,91</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>149,74%</t>
+          <t>131,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>101,45%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 1,18</t>
+          <t>-87,78; -9,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-91,35; -23,62</t>
+          <t>-92,24; -30,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 111,57</t>
+          <t>-7,31; 169,39</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 106,16</t>
+          <t>-25,34; 95,18</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 103,79</t>
+          <t>-23,4; 108,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>66,18; 293,33</t>
+          <t>56,11; 253,92</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 35,97</t>
+          <t>-39,33; 31,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 29,67</t>
+          <t>-44,79; 24,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,39; 160,87</t>
+          <t>48,94; 170,5</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>5,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,97</t>
+          <t>-0,3; 1,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,8</t>
+          <t>-0,46; 0,74</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,81</t>
+          <t>2,53; 4,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,33</t>
+          <t>1,42; 3,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,67</t>
+          <t>0,85; 2,63</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,4</t>
+          <t>6,14; 7,96</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,98</t>
+          <t>0,81; 1,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,57</t>
+          <t>0,48; 1,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,48</t>
+          <t>4,58; 5,79</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>206,2%</t>
+          <t>220,72%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>245,29%</t>
+          <t>270,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>233,43%</t>
+          <t>254,44%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 80,19</t>
+          <t>-18,88; 83,42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 67,84</t>
+          <t>-25,56; 61,66</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>114,76; 338,13</t>
+          <t>132,18; 336,07</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>48,5; 153,73</t>
+          <t>47,55; 151,93</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>28,45; 119,01</t>
+          <t>27,81; 120,08</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>159,65; 341,34</t>
+          <t>196,02; 362,5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>34,84; 110,5</t>
+          <t>35,65; 110,03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>17,68; 88,81</t>
+          <t>20,41; 83,26</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>171,64; 301,54</t>
+          <t>197,55; 333,65</t>
         </is>
       </c>
     </row>
